--- a/users_import_filled.xlsx
+++ b/users_import_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TienSon\Desktop\project\quanlydoan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3E22BC-6915-47EC-B52A-97ADE9787ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C41D27B-DCA3-400C-89C3-5F2E0A55707B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="2772" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1060,7 +1060,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1379,20 +1379,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="32.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="32.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -1466,6 +1466,9 @@
       </c>
       <c r="E3" s="7" t="s">
         <v>301</v>
+      </c>
+      <c r="F3">
+        <v>22103100134</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -1478,7 +1481,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -1504,7 +1507,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -1530,7 +1533,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -1556,7 +1559,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -1582,7 +1585,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1608,7 +1611,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -1634,7 +1637,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
@@ -1660,7 +1663,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1686,7 +1689,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -1712,7 +1715,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
@@ -1738,7 +1741,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>24</v>
       </c>
@@ -1764,7 +1767,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
@@ -1790,7 +1793,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>26</v>
       </c>
@@ -1816,7 +1819,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
@@ -1842,7 +1845,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>28</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>29</v>
       </c>
@@ -1894,7 +1897,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
@@ -1920,7 +1923,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>31</v>
       </c>
@@ -1946,7 +1949,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
@@ -1972,7 +1975,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -1998,7 +2001,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
@@ -2024,7 +2027,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>35</v>
       </c>
@@ -2050,7 +2053,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>36</v>
       </c>
@@ -2076,7 +2079,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>37</v>
       </c>
@@ -2102,7 +2105,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>38</v>
       </c>
@@ -2128,7 +2131,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>39</v>
       </c>
@@ -2154,7 +2157,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>40</v>
       </c>
@@ -2180,7 +2183,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>41</v>
       </c>
@@ -2206,7 +2209,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>42</v>
       </c>
@@ -2232,7 +2235,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>43</v>
       </c>
@@ -2258,7 +2261,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>44</v>
       </c>
@@ -2284,7 +2287,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>45</v>
       </c>
@@ -2310,7 +2313,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>46</v>
       </c>
@@ -2336,7 +2339,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>47</v>
       </c>
@@ -2362,7 +2365,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>48</v>
       </c>
@@ -2388,7 +2391,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>49</v>
       </c>
@@ -2414,7 +2417,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>50</v>
       </c>
@@ -2440,7 +2443,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>51</v>
       </c>
@@ -2466,7 +2469,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>52</v>
       </c>
@@ -2492,7 +2495,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>53</v>
       </c>
@@ -2518,7 +2521,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>54</v>
       </c>
@@ -2544,7 +2547,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>55</v>
       </c>
@@ -2570,7 +2573,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>56</v>
       </c>
@@ -2596,7 +2599,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>57</v>
       </c>
@@ -2622,7 +2625,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>42</v>
       </c>
@@ -2648,7 +2651,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>58</v>
       </c>
@@ -2674,7 +2677,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>59</v>
       </c>
@@ -2700,7 +2703,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>60</v>
       </c>
@@ -2726,7 +2729,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>61</v>
       </c>
@@ -2752,7 +2755,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>62</v>
       </c>
@@ -2778,7 +2781,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>63</v>
       </c>
@@ -2804,7 +2807,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>64</v>
       </c>
@@ -2830,7 +2833,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>65</v>
       </c>
@@ -2856,7 +2859,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>66</v>
       </c>
@@ -2882,7 +2885,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>67</v>
       </c>
@@ -2908,7 +2911,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>68</v>
       </c>
@@ -2934,7 +2937,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>69</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>70</v>
       </c>
@@ -2986,7 +2989,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>71</v>
       </c>
@@ -3012,7 +3015,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>31</v>
       </c>
@@ -3038,7 +3041,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>72</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>73</v>
       </c>
@@ -3090,7 +3093,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>74</v>
       </c>
@@ -3116,7 +3119,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>75</v>
       </c>
@@ -3142,7 +3145,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>76</v>
       </c>
@@ -3168,7 +3171,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>77</v>
       </c>
@@ -3194,7 +3197,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>78</v>
       </c>
@@ -3220,7 +3223,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>79</v>
       </c>
@@ -3246,7 +3249,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>80</v>
       </c>
@@ -3272,7 +3275,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>81</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>82</v>
       </c>
@@ -3324,7 +3327,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>83</v>
       </c>
@@ -3350,7 +3353,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>84</v>
       </c>
@@ -3376,7 +3379,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>85</v>
       </c>
@@ -3402,7 +3405,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>86</v>
       </c>
@@ -3428,7 +3431,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>87</v>
       </c>
@@ -3454,7 +3457,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>88</v>
       </c>
@@ -3480,7 +3483,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>89</v>
       </c>
@@ -3506,7 +3509,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>90</v>
       </c>
@@ -3532,7 +3535,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>91</v>
       </c>
@@ -3558,7 +3561,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>92</v>
       </c>
@@ -3584,7 +3587,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>93</v>
       </c>
@@ -3610,7 +3613,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>94</v>
       </c>
@@ -3636,7 +3639,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>95</v>
       </c>
@@ -3662,7 +3665,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>96</v>
       </c>
@@ -3688,7 +3691,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>97</v>
       </c>
@@ -3714,7 +3717,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>98</v>
       </c>
@@ -3740,7 +3743,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>99</v>
       </c>
@@ -3766,7 +3769,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>100</v>
       </c>
@@ -3792,7 +3795,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>22</v>
       </c>
@@ -3818,7 +3821,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>101</v>
       </c>
@@ -3844,7 +3847,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>68</v>
       </c>
@@ -3870,7 +3873,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>102</v>
       </c>
@@ -3896,7 +3899,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>103</v>
       </c>
@@ -3922,7 +3925,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>78</v>
       </c>
@@ -3948,7 +3951,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>104</v>
       </c>
@@ -3974,7 +3977,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>105</v>
       </c>
@@ -4000,7 +4003,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>106</v>
       </c>
@@ -4026,7 +4029,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>107</v>
       </c>
